--- a/diseases/d238/2026-2029.xlsx
+++ b/diseases/d238/2026-2029.xlsx
@@ -3444,6 +3444,399 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>human-t-lymphotropic-virus-1-or-2-infection</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>人T淋巴细胞嗜性病毒1型或2型感染</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>human-t-lymphotropic-virus-1-or-2-infection</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>人T淋巴细胞嗜性病毒1型或2型感染</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>HTLV 1- och HTLV 2-infektion</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Combined source category; virus type cannot be separated.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3477,7 +3870,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3953,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3570,7 +3963,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -3590,7 +3983,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d238/2026-2029.xlsx
+++ b/diseases/d238/2026-2029.xlsx
@@ -3837,6 +3837,399 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>human-t-lymphotropic-virus-1-or-2-infection</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>人T淋巴细胞嗜性病毒1型或2型感染</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>human-t-lymphotropic-virus-1-or-2-infection</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D238</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Human T-lymphotropic virus 1 or 2 infection</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>人T淋巴细胞嗜性病毒1型或2型感染</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>HTLV 1- och HTLV 2-infektion</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Combined source category; virus type cannot be separated.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HTLV_1_2</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3870,7 +4263,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3953,7 +4346,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -3963,7 +4356,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3983,7 +4376,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -4015,7 +4408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
